--- a/Fase 2/Evidencias Proyecto/04.1 Criterios de  Aceptación - RoomMatch.xlsx
+++ b/Fase 2/Evidencias Proyecto/04.1 Criterios de  Aceptación - RoomMatch.xlsx
@@ -598,7 +598,8 @@
     <t>HU-14</t>
   </si>
   <si>
-    <t>Como estudiante, quiero que la plataforma calcule mi compatibilidad con otros usuarios para identificar posibles roomies.</t>
+    <t xml:space="preserve">Como estudiante, quiero que la plataforma calcule mi compatibilidad con otros usuarios para identificar posibles roomies.
+Parámetros del cálculo: ver anexo 06 (Algoritmo de compatibilidad).</t>
   </si>
   <si>
     <t>CA-14.1</t>
@@ -731,7 +732,7 @@
     <t>HU-17</t>
   </si>
   <si>
-    <t>Como estudiante, quiero confirmar un match con un posible roomie para registrar el inicio de nuestra convivencia.</t>
+    <t xml:space="preserve">Como estudiante buscador u oferente, quiero responder las propuestas de match que me hace RoomMatch para registrar el inicio de nuestra convivencia.</t>
   </si>
   <si>
     <t>CA-17.1</t>
@@ -1359,8 +1360,8 @@
 Entonces esos reportes quedan vinculados a la acción y pasan a «resuelto».</t>
   </si>
   <si>
-    <t>Dado que el estudiante está en el formulario de registro
-Cuando ingresa RUT, nombre, correo, telefono, contraseña y confirmación de contraseña con datos válidos y presiona «Registrarme»
+    <t xml:space="preserve">Dado que el estudiante está en el formulario de registro
+Cuando ingresa RUT, nombre, correo, teléfono, contraseña y confirmación de contraseña con datos válidos y presiona «Registrarme»
 Entonces se crea su cuenta y ve un mensaje de registro exitoso.</t>
   </si>
   <si>
@@ -1369,9 +1370,9 @@
 Entonces encuentra la opción «Reportar perfil» (HU-24).</t>
   </si>
   <si>
-    <t>Dado que ya existe una cuenta con el mismo correo, telefono y RUT
-Cuando el estudiante intenta registrarse con ese correo, telefono o RUT
-Entonces no se crea la cuenta y la plataforma le avisa cuál de los dos datos ya está en uso.</t>
+    <t xml:space="preserve">Dado que ya existe una cuenta con el mismo correo, teléfono o RUT
+Cuando el estudiante intenta registrarse con ese correo, teléfono o RUT
+Entonces no se crea la cuenta y la plataforma le avisa cuál de los datos ya está en uso.</t>
   </si>
   <si>
     <t>Dado que el estudiante completó los campos obligatorios (institución, sede, carrera, dirección, ciudad de origen, región de origen y teléfono)
@@ -1379,65 +1380,83 @@
 Entonces se guarda su perfil y ve un mensaje de confirmación.</t>
   </si>
   <si>
-    <t>Dado que el estudiante indica dónde está el alojamiento
+    <t xml:space="preserve">Dado que el estudiante indica dónde está el alojamiento
 Cuando completa la ubicación
-Entonces debe elegir la comuna de una lista e ingresar el sector(obligatorio) y  dirección de referencia(opcional)</t>
-  </si>
-  <si>
-    <t>Dado que el estudiante está en el listado de alojamientos
-Cuando elige una o más comunas o sectores(zona norte, centro o sur) y aplica el filtro
+Entonces debe elegir la comuna de una lista e ingresar el sector (obligatorio) y la dirección de referencia (opcional).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dado que el estudiante está en el listado de alojamientos
+Cuando elige una o más comunas o sectores (zona norte, centro o sur) y aplica el filtro
 Entonces solo ve publicaciones ubicadas en esas zonas.</t>
   </si>
   <si>
-    <t>Dado que el estudiante abre el filtro de ubicación
+    <t xml:space="preserve">Dado que el estudiante abre el filtro de ubicación
 Cuando revisa las opciones disponibles
-Entonces solo aparecen comunas y sectores(zona norte, centro o sur) que tienen publicaciones activas.</t>
-  </si>
-  <si>
-    <t>Dado que el estudiante tiene preferencias guardadas en su perfil
-Cuando presiona el boton «Guardar como mis preferencias»
+Entonces solo aparecen comunas y sectores (zona norte, centro o sur) que tienen publicaciones activas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dado que el estudiante guardó sus preferencias con «Guardar como mis preferencias»
+Cuando presiona «Usar mis preferencias»
 Entonces los filtros se completan solos con esas preferencias y puede ajustarlos antes de buscar.</t>
   </si>
   <si>
-    <t>Dado que el estudiante quiere destacar una preferencia
-Cuando asigna una categoría (flexible, importante o imprescindible)
-Entonces se guarda con el nivel seleccionado, siendo «importante». Si marca una categoría como «imprescindible», esta tiene mayor peso en el calculo de compatibilidad(HU-14). Permitiendo un max de 3 categorías.</t>
-  </si>
-  <si>
-    <t>Dado que un estudiante activó «Estoy buscando alojamiento», completó el cuestionario y no tiene una convivencia activa, cuando existe un alojamiento activo con cupos cuyo oferente tiene compatibilidad alta (75 % o más) con él, sin conflicto en algo imprescindible, que cumple sus preferencias de búsqueda guardadas y el género que pide la publicación, entonces RoomMatch crea una propuesta de match en estado «sugerido» y avisa a ambos.</t>
-  </si>
-  <si>
-    <t>Dado que existe una propuesta abierta, cuando el buscador y el oferente presionan «Aceptar», en cualquier orden, entonces el match pasa a «confirmado», se crea la convivencia con la fecha de confirmación como inicio, se descuenta un cupo del alojamiento y ambos reciben una notificación. Si solo uno aceptó, la propuesta queda «pendiente» y se avisa al otro</t>
-  </si>
-  <si>
-    <t>Dado que existe una propuesta abierta, cuando cualquiera de los dos presiona «Rechazar» (el motivo es opcional), entonces la propuesta queda «rechazada», no se crea convivencia, el otro recibe una notificación y ese alojamiento no se le vuelve a proponer a ese buscador</t>
-  </si>
-  <si>
-    <t>Dado que un buscador tiene una convivencia confirmada y activa, cuando intenta activar la búsqueda o aceptar otra propuesta, entonces la plataforma no lo permite. El oferente puede tener un match confirmado por cada cupo de su alojamiento.</t>
-  </si>
-  <si>
-    <t>Dado que existe una propuesta abierta, cuando pasan 7 días sin la respuesta de ambos, o el alojamiento se elimina o se queda sin cupos, entonces la propuesta queda «expirada»</t>
-  </si>
-  <si>
-    <t>Sin cambios: después de confirmar el match, ninguno aparece en la lista de posibles roomies del otro.</t>
+    <t xml:space="preserve">Dado que el estudiante quiere destacar una preferencia
+Cuando asigna una importancia a una categoría (flexible, importante o imprescindible)
+Entonces se guarda con el nivel seleccionado; si no elige ninguno, queda «importante». Las categorías «imprescindibles» pesan más en el cálculo de compatibilidad (HU-14) y se pueden marcar como máximo 3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dado que un estudiante activó «Estoy buscando alojamiento», completó el cuestionario y no tiene una convivencia activa
+Cuando existe un alojamiento activo con cupos cuyo oferente tiene compatibilidad alta (75 % o más) con él, sin conflicto en algo imprescindible, que cumple sus preferencias de búsqueda guardadas y el género que pide la publicación
+Entonces RoomMatch crea una propuesta de match en estado «sugerido» y avisa a ambos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dado que existe una propuesta abierta
+Cuando el buscador y el oferente presionan «Aceptar», en cualquier orden
+Entonces el match pasa a «confirmado», se crea la convivencia con la fecha de confirmación como inicio, se descuenta un cupo del alojamiento y ambos reciben una notificación. Si solo uno aceptó, la propuesta queda «pendiente» y se avisa al otro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dado que existe una propuesta abierta
+Cuando cualquiera de los dos presiona «Rechazar» (el motivo es opcional)
+Entonces la propuesta queda «rechazada», no se crea convivencia, el otro recibe una notificación y ese alojamiento no se le vuelve a proponer a ese buscador.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dado que un buscador tiene una convivencia confirmada y activa
+Cuando intenta activar la búsqueda o aceptar otra propuesta
+Entonces la plataforma no lo permite. El oferente puede tener un match confirmado por cada cupo de su alojamiento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dado que existe una propuesta abierta
+Cuando pasan 7 días sin la respuesta de ambos, o el alojamiento se elimina o se queda sin cupos
+Entonces la propuesta queda «expirada».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dado que un match fue confirmado
+Cuando cualquiera de los dos estudiantes revisa la lista de posibles roomies (HU-15)
+Entonces ya no aparece el otro como posible roomie, porque su convivencia quedó registrada.</t>
   </si>
   <si>
     <t>CA-17.7</t>
   </si>
   <si>
-    <t>Dado que un buscador tiene la búsqueda activa, cuando RoomMatch genera propuestas, entonces tiene como máximo 3 abiertas a la vez, ordenadas de mayor a menor compatibilidad y con un solo alojamiento por oferente.</t>
+    <t xml:space="preserve">Dado que un buscador tiene la búsqueda activa
+Cuando RoomMatch genera propuestas
+Entonces tiene como máximo 3 abiertas a la vez, ordenadas de mayor a menor compatibilidad y con un solo alojamiento por oferente.</t>
   </si>
   <si>
     <t>CA-17.8</t>
   </si>
   <si>
-    <t>Dado que se confirmó el match de un buscador, cuando termina la confirmación, entonces se cierran sus demás propuestas abiertas y su búsqueda se desactiva. Si el alojamiento se quedó sin cupos, pasa a «completa» y se cierran las propuestas que tenía con otros buscadoresDado que se confirmó el match de un buscador, cuando termina la confirmación, entonces se cierran sus demás propuestas abiertas y su búsqueda se desactiva. Si el alojamiento se quedó sin cupos, pasa a «completa» y se cierran las propuestas que tenía con otros buscadores</t>
+    <t xml:space="preserve">Dado que se confirmó el match de un buscador
+Cuando termina la confirmación
+Entonces se cierran sus demás propuestas abiertas y su búsqueda se desactiva. Si el alojamiento se quedó sin cupos, pasa a «completa» y se cierran las propuestas que tenía con otros buscadores.</t>
   </si>
   <si>
     <t>CA-13.6</t>
   </si>
   <si>
-    <t>el cuestionario es obligatorio justo después de registrarse. Mientras no se complete, no se puede entrar al resto de la plataformael cuestionario es obligatorio justo después de registrarse. Mientras no se complete, no se puede entrar al resto de la plataforma</t>
+    <t xml:space="preserve">Dado que el estudiante acaba de registrarse
+Cuando intenta entrar a cualquier página de la plataforma
+Entonces primero debe completar el cuestionario de hábitos; mientras no lo complete, no puede usar el resto de la plataforma.</t>
   </si>
   <si>
     <t>Dado que el estudiante respondió que la convivencia no está funcionando
@@ -1453,7 +1472,9 @@
     <t>CA-14.6</t>
   </si>
   <si>
-    <t>Dado que dos estudiantes chocan en una categoría que alguno marcó como imprescindible, cuando se calcula su compatibilidad, entonces el par queda descartado y no aparece en «Posibles roomies» ni recibe propuestas de match.</t>
+    <t xml:space="preserve">Dado que dos estudiantes chocan en una categoría que alguno marcó como imprescindible
+Cuando se calcula su compatibilidad
+Entonces el par queda descartado y no aparece en «Posibles roomies» ni recibe propuestas de match.</t>
   </si>
 </sst>
 </file>
@@ -1831,7 +1852,7 @@
       </c>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:6" ht="69" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>4</v>
       </c>
@@ -1847,7 +1868,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="69" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="82.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15"/>
       <c r="B3" s="15"/>
       <c r="C3" s="3" t="s">
@@ -2167,7 +2188,7 @@
       <c r="E27" s="5"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="82.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15"/>
       <c r="B28" s="15"/>
       <c r="C28" s="7" t="s">
@@ -2471,7 +2492,7 @@
       <c r="E51" s="5"/>
       <c r="F51" s="6"/>
     </row>
-    <row r="52" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="82.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
         <v>120</v>
       </c>
@@ -2551,7 +2572,7 @@
       <c r="E57" s="5"/>
       <c r="F57" s="6"/>
     </row>
-    <row r="58" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="69.0" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="15"/>
       <c r="B58" s="15"/>
       <c r="C58" s="7" t="s">
@@ -2639,7 +2660,7 @@
       <c r="E64" s="5"/>
       <c r="F64" s="6"/>
     </row>
-    <row r="65" spans="1:6" ht="82.8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="15"/>
       <c r="B65" s="15"/>
       <c r="C65" s="3" t="s">
@@ -2663,7 +2684,7 @@
       <c r="E66" s="5"/>
       <c r="F66" s="6"/>
     </row>
-    <row r="67" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="82.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="15"/>
       <c r="B67" s="15"/>
       <c r="C67" s="3" t="s">
@@ -2739,7 +2760,7 @@
       <c r="E72" s="5"/>
       <c r="F72" s="6"/>
     </row>
-    <row r="73" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="69.0" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="15"/>
       <c r="B73" s="15"/>
       <c r="C73" s="7" t="s">
@@ -2879,7 +2900,7 @@
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
     </row>
-    <row r="84" spans="1:6" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="138.0" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="16" t="s">
         <v>187</v>
       </c>
@@ -2895,7 +2916,7 @@
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
     </row>
-    <row r="85" spans="1:6" ht="82.8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="15"/>
       <c r="B85" s="15"/>
       <c r="C85" s="3" t="s">
@@ -2907,7 +2928,7 @@
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
     </row>
-    <row r="86" spans="1:6" ht="69" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="15"/>
       <c r="B86" s="15"/>
       <c r="C86" s="3" t="s">
@@ -2919,7 +2940,7 @@
       <c r="E86" s="6"/>
       <c r="F86" s="6"/>
     </row>
-    <row r="87" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" ht="96.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="15"/>
       <c r="B87" s="15"/>
       <c r="C87" s="3" t="s">
@@ -2931,7 +2952,7 @@
       <c r="E87" s="6"/>
       <c r="F87" s="6"/>
     </row>
-    <row r="88" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="15"/>
       <c r="B88" s="15"/>
       <c r="C88" s="3" t="s">
@@ -2943,7 +2964,7 @@
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
     </row>
-    <row r="89" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="69.0" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="15"/>
       <c r="B89" s="15"/>
       <c r="C89" s="3" t="s">
@@ -2955,7 +2976,7 @@
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
     </row>
-    <row r="90" spans="1:6" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" ht="69.0" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="15"/>
       <c r="B90" s="15"/>
       <c r="C90" s="3" t="s">
